--- a/artfynd/A 28620-2020 artfynd.xlsx
+++ b/artfynd/A 28620-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28620-2020 artfynd.xlsx
+++ b/artfynd/A 28620-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>87503639</v>
+        <v>87503674</v>
       </c>
       <c r="B17" t="n">
-        <v>77177</v>
+        <v>78072</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>368260.0939467277</v>
+        <v>368241.1990116842</v>
       </c>
       <c r="R17" t="n">
-        <v>6858191.035993362</v>
+        <v>6858179.943459211</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>87503674</v>
+        <v>87503675</v>
       </c>
       <c r="B18" t="n">
-        <v>78072</v>
+        <v>76909</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>87503675</v>
+        <v>87503611</v>
       </c>
       <c r="B19" t="n">
-        <v>76909</v>
+        <v>77258</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>368241.1990116842</v>
+        <v>368120.1017533364</v>
       </c>
       <c r="R19" t="n">
-        <v>6858179.943459211</v>
+        <v>6858207.779253729</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>87503611</v>
+        <v>87503618</v>
       </c>
       <c r="B20" t="n">
-        <v>77258</v>
+        <v>90657</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,25 +2703,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>368120.1017533364</v>
+        <v>368062.1615496859</v>
       </c>
       <c r="R20" t="n">
-        <v>6858207.779253729</v>
+        <v>6858191.10136375</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>87503618</v>
+        <v>87503663</v>
       </c>
       <c r="B21" t="n">
-        <v>90657</v>
+        <v>76909</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2815,25 +2815,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4365</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>368062.1615496859</v>
+        <v>368226.12311595</v>
       </c>
       <c r="R21" t="n">
-        <v>6858191.10136375</v>
+        <v>6858181.94278327</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2915,7 +2915,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>87503663</v>
+        <v>87503627</v>
       </c>
       <c r="B22" t="n">
         <v>76909</v>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>368226.12311595</v>
+        <v>368016.1300342458</v>
       </c>
       <c r="R22" t="n">
-        <v>6858181.94278327</v>
+        <v>6858384.837133607</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>87503627</v>
+        <v>87503689</v>
       </c>
       <c r="B23" t="n">
-        <v>76909</v>
+        <v>77177</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3043,21 +3043,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>368016.1300342458</v>
+        <v>368164.1835531709</v>
       </c>
       <c r="R23" t="n">
-        <v>6858384.837133607</v>
+        <v>6858208.916504369</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>87503689</v>
+        <v>87503719</v>
       </c>
       <c r="B24" t="n">
-        <v>77177</v>
+        <v>77258</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>368164.1835531709</v>
+        <v>367994.9775778968</v>
       </c>
       <c r="R24" t="n">
-        <v>6858208.916504369</v>
+        <v>6858339.792297403</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>87503719</v>
+        <v>87503664</v>
       </c>
       <c r="B25" t="n">
-        <v>77258</v>
+        <v>78072</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>367994.9775778968</v>
+        <v>368011.0856160457</v>
       </c>
       <c r="R25" t="n">
-        <v>6858339.792297403</v>
+        <v>6858290.944603465</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>87503664</v>
+        <v>87503729</v>
       </c>
       <c r="B26" t="n">
-        <v>78072</v>
+        <v>77605</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>368011.0856160457</v>
+        <v>368110.1360437655</v>
       </c>
       <c r="R26" t="n">
-        <v>6858290.944603465</v>
+        <v>6858207.217943328</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3475,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>87503729</v>
+        <v>87503710</v>
       </c>
       <c r="B27" t="n">
-        <v>77605</v>
+        <v>78072</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3491,21 +3491,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>967</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>368110.1360437655</v>
+        <v>368087.8398391614</v>
       </c>
       <c r="R27" t="n">
-        <v>6858207.217943328</v>
+        <v>6858193.893351057</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3587,10 +3587,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>87503710</v>
+        <v>87503682</v>
       </c>
       <c r="B28" t="n">
-        <v>78072</v>
+        <v>76909</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3603,21 +3603,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>368087.8398391614</v>
+        <v>368032.2243137693</v>
       </c>
       <c r="R28" t="n">
-        <v>6858193.893351057</v>
+        <v>6858396.981397429</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>87503682</v>
+        <v>87503681</v>
       </c>
       <c r="B29" t="n">
-        <v>76909</v>
+        <v>78072</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3715,21 +3715,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>87503681</v>
+        <v>87503695</v>
       </c>
       <c r="B30" t="n">
-        <v>78072</v>
+        <v>77177</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3827,21 +3827,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>368032.2243137693</v>
+        <v>367981.1053771205</v>
       </c>
       <c r="R30" t="n">
-        <v>6858396.981397429</v>
+        <v>6858372.950873099</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3923,7 +3923,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>87503695</v>
+        <v>87503650</v>
       </c>
       <c r="B31" t="n">
         <v>77177</v>
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>367981.1053771205</v>
+        <v>368070.8297980403</v>
       </c>
       <c r="R31" t="n">
-        <v>6858372.950873099</v>
+        <v>6858391.236644194</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4035,7 +4035,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>87503650</v>
+        <v>87503630</v>
       </c>
       <c r="B32" t="n">
         <v>77177</v>
@@ -4075,10 +4075,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>368070.8297980403</v>
+        <v>368077.9167731488</v>
       </c>
       <c r="R32" t="n">
-        <v>6858391.236644194</v>
+        <v>6858304.914005334</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4147,10 +4147,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>87503630</v>
+        <v>87503688</v>
       </c>
       <c r="B33" t="n">
-        <v>77177</v>
+        <v>89545</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4159,25 +4159,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4187,10 +4187,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>368077.9167731488</v>
+        <v>368164.2377747457</v>
       </c>
       <c r="R33" t="n">
-        <v>6858304.914005334</v>
+        <v>6858198.039628766</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4259,10 +4259,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>87503688</v>
+        <v>87503727</v>
       </c>
       <c r="B34" t="n">
-        <v>89545</v>
+        <v>77259</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4271,25 +4271,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>368164.2377747457</v>
+        <v>368110.1360437655</v>
       </c>
       <c r="R34" t="n">
-        <v>6858198.039628766</v>
+        <v>6858207.217943328</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4371,10 +4371,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>87503727</v>
+        <v>87503625</v>
       </c>
       <c r="B35" t="n">
-        <v>77259</v>
+        <v>78072</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>368110.1360437655</v>
+        <v>368016.1300342458</v>
       </c>
       <c r="R35" t="n">
-        <v>6858207.217943328</v>
+        <v>6858384.837133607</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4483,7 +4483,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>87503625</v>
+        <v>87672091</v>
       </c>
       <c r="B36" t="n">
         <v>78072</v>
@@ -4517,16 +4517,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tranutjärn, Dlr</t>
+          <t>Lövåsen, O tjärn NV om Stora Karmortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>368016.1300342458</v>
+        <v>367926.4899712853</v>
       </c>
       <c r="R36" t="n">
-        <v>6858384.837133607</v>
+        <v>6858307.449296223</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4553,7 +4556,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2020-08-10</t>
+          <t>2020-08-24</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -4563,7 +4566,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2020-08-10</t>
+          <t>2020-08-24</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -4577,28 +4580,59 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Lavtallskog</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>brandpräglad</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # 3 m hög brandstubbe # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>87672091</v>
+        <v>87672164</v>
       </c>
       <c r="B37" t="n">
-        <v>78072</v>
+        <v>77177</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4611,21 +4645,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4638,10 +4672,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>367926.4899712853</v>
+        <v>367905.576913854</v>
       </c>
       <c r="R37" t="n">
-        <v>6858307.449296223</v>
+        <v>6858305.420212433</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4706,24 +4740,14 @@
           <t>brandpräglad</t>
         </is>
       </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # 3 m hög brandstubbe # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4741,10 +4765,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>87672164</v>
+        <v>87830821</v>
       </c>
       <c r="B38" t="n">
-        <v>77177</v>
+        <v>89323</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4753,25 +4777,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>2013</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4780,17 +4804,17 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lövåsen, O tjärn NV om Stora Karmortjärnen, Dlr</t>
+          <t>Karmortjärn, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>367905.576913854</v>
+        <v>368111.5244840082</v>
       </c>
       <c r="R38" t="n">
-        <v>6858305.420212433</v>
+        <v>6858341.441774791</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4814,7 +4838,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2020-09-04</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -4824,12 +4848,17 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2020-09-04</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Hexagoniska porer som gick ut i kanten, mjuk fruktkropp, grå ton men f.viticola är nog inte helt utesluten. Kollekt taget.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4842,45 +4871,40 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Lavtallskog</t>
-        </is>
-      </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>brandpräglad</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>tallnaturskog</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>Kelolåga tall men växte utanför själva kolet.</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact</t>
+          <t>Kelolåga tall men växte utanför själva kolet.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>87830821</v>
+        <v>90731426</v>
       </c>
       <c r="B39" t="n">
-        <v>89323</v>
+        <v>90841</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4889,44 +4913,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2013</v>
+        <v>2079</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Karmortjärn, Dlr</t>
+          <t>Hundfjället, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>368111.5244840082</v>
+        <v>368056.8097879633</v>
       </c>
       <c r="R39" t="n">
-        <v>6858341.441774791</v>
+        <v>6858396.032694572</v>
       </c>
       <c r="S39" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4950,7 +4971,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -4960,7 +4981,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -4968,35 +4989,14 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Hexagoniska porer som gick ut i kanten, mjuk fruktkropp, grå ton men f.viticola är nog inte helt utesluten. Kollekt taget.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>tallnaturskog</t>
-        </is>
-      </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>Kelolåga tall men växte utanför själva kolet.</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Kelolåga tall men växte utanför själva kolet.</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5010,118 +5010,6 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>90731426</v>
-      </c>
-      <c r="B40" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>2079</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Nordtagging</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Odonticium romellii</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Hundfjället, Dlr</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>368056.8097879633</v>
-      </c>
-      <c r="R40" t="n">
-        <v>6858396.032694572</v>
-      </c>
-      <c r="S40" t="n">
-        <v>5</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Idre</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
